--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
@@ -320,11 +320,11 @@
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="0"/>
         </c:dLbls>
-        <c:axId val="1763042762"/>
         <c:axId val="1906877268"/>
+        <c:axId val="1053878294"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1763042762"/>
+        <c:axId val="1906877268"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -381,12 +381,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1906877268"/>
+        <c:crossAx val="1053878294"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1906877268"/>
+        <c:axId val="1053878294"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -443,7 +443,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1763042762"/>
+        <c:crossAx val="1906877268"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1053,7 +1053,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e544301d-9c24-412a-928a-d5f3feb51f66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a7ebf3d0-d14d-48a6-b8e8-60804954ddc9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
@@ -320,11 +320,11 @@
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="0"/>
         </c:dLbls>
-        <c:axId val="1906877268"/>
-        <c:axId val="1053878294"/>
+        <c:axId val="1370794819"/>
+        <c:axId val="84907464"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1906877268"/>
+        <c:axId val="1370794819"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -381,12 +381,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1053878294"/>
+        <c:crossAx val="84907464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1053878294"/>
+        <c:axId val="84907464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -443,7 +443,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1906877268"/>
+        <c:crossAx val="1370794819"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1053,7 +1053,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a7ebf3d0-d14d-48a6-b8e8-60804954ddc9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ae56444-080b-4939-b42a-7ed65b26c93c}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Scatter Chart_report.xlsx
@@ -320,11 +320,11 @@
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="0"/>
         </c:dLbls>
+        <c:axId val="469126741"/>
         <c:axId val="1370794819"/>
-        <c:axId val="84907464"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1370794819"/>
+        <c:axId val="469126741"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -381,12 +381,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84907464"/>
+        <c:crossAx val="1370794819"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="84907464"/>
+        <c:axId val="1370794819"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -443,7 +443,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370794819"/>
+        <c:crossAx val="469126741"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1053,7 +1053,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ae56444-080b-4939-b42a-7ed65b26c93c}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3b1843f8-5b50-4333-95b6-2d67e8a8b0af}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
